--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -36,12 +36,12 @@
     <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
+    <t xml:space="preserve">Ñiquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
-    <t xml:space="preserve">Ñiquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ninhue</t>
   </si>
   <si>
@@ -66,12 +66,12 @@
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,13 +535,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>16202</v>
+        <v>16303</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>172.63</v>
+        <v>187.65</v>
       </c>
     </row>
     <row r="3">
@@ -552,13 +552,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16303</v>
+        <v>16202</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>172.47</v>
+        <v>185.69</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>154.36</v>
+        <v>165.67</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>150.23</v>
+        <v>162.58</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>145.52</v>
+        <v>157.01</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>136.1</v>
+        <v>150.71</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>134.53</v>
+        <v>144.97</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>128.58</v>
+        <v>138.6</v>
       </c>
     </row>
     <row r="10">
@@ -677,7 +677,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>127.31</v>
+        <v>138.18</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>124.53</v>
+        <v>135.07</v>
       </c>
     </row>
     <row r="12">
@@ -705,13 +705,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16305</v>
+        <v>16108</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>118.64</v>
+        <v>128.07</v>
       </c>
     </row>
     <row r="13">
@@ -722,13 +722,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>16108</v>
+        <v>16305</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>118.51</v>
+        <v>127.98</v>
       </c>
     </row>
     <row r="14">
@@ -745,7 +745,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>117.11</v>
+        <v>125.12</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>112.26</v>
+        <v>120.95</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110.1</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="17">
@@ -796,7 +796,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>109.62</v>
+        <v>118.54</v>
       </c>
     </row>
     <row r="18">
@@ -813,7 +813,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>105.73</v>
+        <v>113.96</v>
       </c>
     </row>
     <row r="19">
@@ -830,7 +830,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>104.12</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="20">
@@ -847,7 +847,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>98.26</v>
+        <v>106.04</v>
       </c>
     </row>
     <row r="21">
@@ -864,7 +864,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>88.2</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="22">
@@ -881,7 +881,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>71.58</v>
+        <v>76.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Portezuelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Treguaco</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:15</t>
+    <t xml:space="preserve">2026-10-04 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:40</t>
+    <t xml:space="preserve">2026-10-05 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
